--- a/resource-mapping/HoyaDocs_Resource_Mapping.xlsx
+++ b/resource-mapping/HoyaDocs_Resource_Mapping.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +66,29 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFCCCCCC"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +193,27 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +699,7 @@
 physeo-phys 5.05 Hormones</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -711,7 +758,7 @@
 physeo-phys 5.05 Hormones</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -776,7 +823,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -839,7 +886,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -915,7 +962,7 @@
 physeo-phys 5.04 Gallbladder</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -983,7 +1030,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1043,7 +1090,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1121,7 +1168,7 @@
 physeo-phys 5.06 Satiety &amp; Hunger</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1195,7 +1242,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1262,7 +1309,7 @@
 physeo-phys 5.04 Gallbladder</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1335,7 +1382,7 @@
 physeo-phys 5.04 Gallbladder</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1421,9 +1468,10 @@
 physeo-path 6.04 Stomach</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 5.09 09 Helicobacter pylori
+Xref: sketchy-micro 3.01 01 Candida albicans</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1495,7 +1543,7 @@
 physeo-phys 5.02 Exocrine Pancreas &amp; Metabolism</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1604,9 +1652,11 @@
 physeo-path 6.09 Colon Polyps Carcinoma</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 1.02 02 Entamoeba histolytica
+Xref: sketchy-micro 1.07 07 Streptococcus gallolyticus (Group D Strep)
+Xref: sketchy-micro 3.01 01 Trypanosoma cruzi</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1731,9 +1781,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>sketchy-pharm 1.01 Antiemetic Agents</t>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>sketchy-pharm 1.01 Antiemetic Agents
+Xref: sketchy-micro 2.03 03 Clostridium botulinum
+Xref: sketchy-micro 2.04 04 Clostridium perfringens</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1797,7 +1849,7 @@
 physeo-path 6.09 Colon Polyps Carcinoma</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1877,12 +1929,13 @@
 physeo-pharm 11.13 Aprepitant</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.01 Antiemetic Agents
 sketchy-pharm 1.02 H2 Receptor Blockers &amp; PPIs
 sketchy-pharm 1.03 Laxatives
-sketchy-pharm 1.04 Antidiarrheal Agents</t>
+sketchy-pharm 1.04 Antidiarrheal Agents
+Xref: sketchy-micro 5.09 09 Helicobacter pylori</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1945,23 +1998,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>sketchy-micro 2.03 Clostridium botulinum
-sketchy-micro 2.04 Clostridium perfringens
-sketchy-micro 2.05 Clostridioides difficile
-sketchy-micro 2.07 Listeria monocytogenes
-sketchy-micro 5.02 Salmonella Part 1 Introduction to Salmonella &amp; NTS 02 Salmonella Part 1 Introduction to Salmonella &amp; NTS
-sketchy-micro 5.03 Salmonella Part 2 Typhoidal Salmonella 03 Salmonella Part 2 Typhoidal Salmonella
-sketchy-micro 5.04 Shigella spp.
-sketchy-micro 5.05 Escherichia coli (ETEC, EHEC)
-sketchy-micro 5.06 Yersinia enterocolitica &amp; pestis
-sketchy-micro 5.07 Campylobacter jejuni
-sketchy-micro 5.08 Vibrio spp.
-sketchy-micro 5.09 Helicobacter pylori
-sketchy-micro 11.01 Clostridioides difficile [Old Version]
-sketchy-micro 11.05 Vibrio spp. [Old Version]
-sketchy-micro 11.06 Salmonella enteritidis &amp; typhi [Retired Video]</t>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.01 01 Bacillus anthracis &amp; cereus
+sketchy-micro 2.03 03 Clostridium botulinum
+sketchy-micro 2.04 04 Clostridium perfringens
+sketchy-micro 2.05 05 Clostridioides difficile
+sketchy-micro 2.07 07 Listeria monocytogenes
+sketchy-micro 5.01 01 Klebsiella pneumoniae, Enterobacter spp., Serratia marcescens
+sketchy-micro 5.02 02 Salmonella Part 1 Introduction to Salmonella &amp; NTS
+sketchy-micro 5.03 03 Salmonella Part 2 Typhoidal Salmonella
+sketchy-micro 5.04 04 Shigella spp.
+sketchy-micro 5.05 05 Escherichia coli (ETEC, EHEC)
+sketchy-micro 5.06 06 Yersinia enterocolitica &amp; pestis
+sketchy-micro 5.07 07 Campylobacter jejuni
+sketchy-micro 5.08 08 Vibrio spp.
+sketchy-micro 5.09 09 Helicobacter pylori
+sketchy-micro 1.05 05 Hepatitis A Virus (PicoRNAviridae)
+sketchy-micro 1.06 06 Norovirus &amp; Norwalk Virus (Caliciviridae)
+sketchy-micro 2.08 08 Rotavirus &amp; Colorado Tick Fever Virus (Reoviridae)
+sketchy-micro 11.01 01 Clostridioides difficile [Old Version]
+sketchy-micro 11.05 05 Vibrio spp. [Old Version]
+sketchy-micro 11.06 06 Salmonella enteritidis &amp; typhi [Retired Video]
+Xref: sketchy-micro 1.07 07 Streptococcus gallolyticus (Group D Strep)</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -2019,9 +2078,17 @@
           <t>physeo-pharm 3.01 Malathion, Permethrin, &amp; Lindane</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.01 Klebsiella pneumoniae, Enterobacter spp., Serratia marcescens</t>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.01 01 Giardia lamblia
+sketchy-micro 1.02 02 Entamoeba histolytica
+sketchy-micro 1.03 03 Cryptosporidium spp.
+sketchy-micro 5.01 01 Intestinal Nematodes - Enterobius, Ancylostoma, Necator, Ascaris, Strongyloides, and Trichinella
+sketchy-micro FAadd Trichuris trichiura (whipworm)
+sketchy-micro 6.01 01 Cestodes
+sketchy-micro 6.02 02 Trematodes
+Xref: sketchy-micro 2.01 01 Toxoplasma gondii
+Xref: sketchy-micro 3.01 01 Trypanosoma cruzi</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -2086,7 +2153,7 @@
 physeo-path 6.09 Colon Polyps Carcinoma</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2140,7 +2207,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2193,7 +2260,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2279,9 +2346,18 @@
 physeo-path 6.14 Other Liver Conditions</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.05 05 Hepatitis A Virus (PicoRNAviridae)
+sketchy-micro 1.08 08 Hepatitis C Virus (Flaviviridae)
+sketchy-micro 3.12 12 Hepatitis B Viral Basics &amp; Infectious Diseases (Hepadnaviridae)
+sketchy-micro 3.13 13 Hepatitis B Viral Life Cycle (Hepadnaviridae)
+sketchy-micro 4.01 01 Hepatitis A Virus (PicoRNAviridae) [Old Version]
+sketchy-micro 4.02 02 Hepatitis B Virus (HepaDNAviridae) [Old Version]
+sketchy-micro 4.03 03 Hepatitis C Virus (Flaviviridae) [Old Version]
+Xref: sketchy-micro 1.02 02 Entamoeba histolytica
+Xref: sketchy-micro 6.02 02 Trematodes
+Xref: sketchy-micro 3.02 02 Aspergillus fumigatus</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2361,7 +2437,7 @@
           <t>physeo-phys 5.03 Liver &amp; Bilirubin Metabolism</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2423,7 +2499,7 @@
           <t>physeo-path 6.10 Pancreas</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2498,7 +2574,7 @@
           <t>physeo-path 6.11 Gallbladder Biliary Tract</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2560,9 +2636,10 @@
 physeo-phys 5.02 Exocrine Pancreas &amp; Metabolism</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 5.08 08 Vibrio spp.
+Xref: sketchy-micro 11.05 05 Vibrio spp. [Old Version]</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -16543,97 +16620,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Subchapter</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Learning Objectives</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Runtime (min)</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Anki Cards</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>Anki Tag</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="20" t="inlineStr">
         <is>
           <t>UWorld QIDs</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.01 Antiemetic Agents</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Poisoning Conference and Cases</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Identify the symptoms observed with agents involved in common poisoning exposures.
 Identify the time course of symptom presentation following exposure to agents involved in</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyPharm::05_GI_&amp;_Endocrine::01_GI::01_Antiemetic_Agents</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="G2" s="21" t="n"/>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.01 Antiemetic Agents</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>State the possible targets for control of gastric acid and the classes of drugs (and
 Explain the use of triple or quadruple therapy in the treatment of H. pylori
@@ -16643,31 +16720,31 @@
 Discuss the differences in biologic agents used to treat inflammatory bowel</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyPharm::05_GI_&amp;_Endocrine::01_GI::01_Antiemetic_Agents</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr"/>
+      <c r="G3" s="21" t="n"/>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.02 H2 Receptor Blockers &amp; PPIs</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>State the possible targets for control of gastric acid and the classes of drugs (and
 Explain the use of triple or quadruple therapy in the treatment of H. pylori
@@ -16677,31 +16754,31 @@
 Discuss the differences in biologic agents used to treat inflammatory bowel</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyPharm::05_GI_&amp;_Endocrine::01_GI::02_H2_Receptor_Blockers_&amp;_PPIs</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="G4" s="21" t="n"/>
     </row>
     <row r="5" ht="84" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.03 Laxatives</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>State the possible targets for control of gastric acid and the classes of drugs (and
 Explain the use of triple or quadruple therapy in the treatment of H. pylori
@@ -16711,31 +16788,31 @@
 Discuss the differences in biologic agents used to treat inflammatory bowel</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyPharm::05_GI_&amp;_Endocrine::01_GI::03_Laxatives</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="G5" s="21" t="n"/>
     </row>
     <row r="6" ht="84" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>sketchy-pharm 1.04 Antidiarrheal Agents</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>State the possible targets for control of gastric acid and the classes of drugs (and
 Explain the use of triple or quadruple therapy in the treatment of H. pylori
@@ -16745,47 +16822,78 @@
 Discuss the differences in biologic agents used to treat inflammatory bowel</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr"/>
-      <c r="E6" s="11" t="n">
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyPharm::05_GI_&amp;_Endocrine::01_GI::04_Antidiarrheal_Agents</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="21" t="n"/>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 2.03 Clostridium botulinum</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.01 01 Bacillus anthracis &amp; cereus</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::01_Bacillus_anthracis_&amp;_cereus</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="84" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.03 03 Clostridium botulinum</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Review the different pathogens that cause infectious diarrhea
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
+Review the clinical manifestations of common intraabdominal infections</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E8" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::03_Clostridium_botulinum</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>QID 1397: Clostridium difficile infection
 QID 1398: Clostridium difficile infection
@@ -16796,36 +16904,36 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="84" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 2.04 Clostridium perfringens</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+    <row r="9" ht="84" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.04 04 Clostridium perfringens</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E9" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::04_Clostridium_perfringens</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>QID 1397: Clostridium difficile infection
 QID 1398: Clostridium difficile infection
@@ -16836,36 +16944,36 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 2.05 Clostridioides difficile</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.05 05 Clostridioides difficile</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E10" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::05_Clostridioides_difficile</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>QID 1397: Clostridium difficile infection
 QID 1398: Clostridium difficile infection
@@ -16876,297 +16984,431 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 2.07 Listeria monocytogenes</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.07 07 Listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D11" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E11" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::07_Listeria_monocytogenes</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.02 Salmonella Part 1 Introduction to Salmonella &amp; NTS 02 Salmonella Part 1 Introduction to Salmonella &amp; NTS</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="G11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.01 01 Klebsiella pneumoniae, Enterobacter spp., Serratia marcescens</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.03 Salmonella Part 2 Typhoidal Salmonella 03 Salmonella Part 2 Typhoidal Salmonella</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="D12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::01_Klebsiella_pneumoniae,_Enterobacter_spp.,_Serratia_marcescens</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.02 02 Salmonella Part 1 Introduction to Salmonella &amp; NTS</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr"/>
-      <c r="E12" s="11" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.04 Shigella spp.</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="D13" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::02_Salmonella_Part_1_Introduction_to_Salmonella_&amp;_NTS</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.03 03 Salmonella Part 2 Typhoidal Salmonella</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D14" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::03_Salmonella_Part_2_Typhoidal_Salmonella</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.04 04 Shigella spp.</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Review the different pathogens that cause infectious diarrhea
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
+Review the clinical manifestations of common intraabdominal infections</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E15" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::04_Shigella_spp.</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.05 Escherichia coli (ETEC, EHEC)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="G15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.05 05 Escherichia coli (ETEC, EHEC)</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D16" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E16" s="21" t="n">
         <v>34</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::05_Escherichia_coli_(ETEC,_EHEC)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.06 Yersinia enterocolitica &amp; pestis</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="G16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.06 06 Yersinia enterocolitica &amp; pestis</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D17" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E17" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::06_Yersinia_enterocolitica_&amp;_pestis</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.07 Campylobacter jejuni</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="G17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.07 07 Campylobacter jejuni</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D18" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E18" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::07_Campylobacter_jejuni</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.08 Vibrio spp.</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="G18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="84" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.08 08 Vibrio spp.</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D19" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E19" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::08_Vibrio_spp.</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.09 Helicobacter pylori</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="G19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.09 09 Helicobacter pylori</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D20" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E20" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::09_Helicobacter_pylori</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 11.01 Clostridioides difficile [Old Version]</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="G20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.05 05 Hepatitis A Virus (PicoRNAviridae)</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="n">
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::01_RNA_(+)_Sense::05_Hepatitis_A_Virus_(PicoRNAviridae)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.06 06 Norovirus &amp; Norwalk Virus (Caliciviridae)</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Review the different pathogens that cause infectious diarrhea
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
+Review the clinical manifestations of common intraabdominal infections</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::01_RNA_(+)_Sense::06_Norovirus_&amp;_Norwalk_Virus_(Caliciviridae)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 2.08 08 Rotavirus &amp; Colorado Tick Fever Virus (Reoviridae)</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Review the different pathogens that cause infectious diarrhea
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
+Review the clinical manifestations of common intraabdominal infections</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::02_RNA_(-)_Sense::08_Rotavirus_&amp;_Colorado_Tick_Fever_Virus_(Reoviridae)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 11.01 01 Clostridioides difficile [Old Version]</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Review the different pathogens that cause infectious diarrhea
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
+Review the clinical manifestations of common intraabdominal infections</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::11_Retired_Lessons::01_Clostridioides_difficile_[Old_Version]</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>QID 1397: Clostridium difficile infection
 QID 1398: Clostridium difficile infection
@@ -17177,94 +17419,929 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 11.05 Vibrio spp. [Old Version]</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 11.05 05 Vibrio spp. [Old Version]</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr"/>
-      <c r="E20" s="11" t="n">
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::11_Retired_Lessons::05_Vibrio_spp._[Old_Version]</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>sketchy-micro 11.06 Salmonella enteritidis &amp; typhi [Retired Video]</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="G25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 11.06 06 Salmonella enteritidis &amp; typhi [Retired Video]</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>GI Infections</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>Review the different pathogens that cause infectious diarrhea
-Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler’s diarrhea, and C. difficile
+Understand the different clinical manifestations of and pathogens that cause watery diarrhea, dysentery, food poisoning, traveler's diarrhea, and C. difficile
 Review the clinical manifestations of common intraabdominal infections</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="13" t="n">
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::11_Retired_Lessons::06_Salmonella_enteritidis_&amp;_typhi_[Retired_Video]</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>sketchy-micro 5.01 Klebsiella pneumoniae, Enterobacter spp., Serratia marcescens</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="G26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 1.07 07 Streptococcus gallolyticus (Group D Strep)</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>GI Infections</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 07 Streptococcus gallolyticus (Group D Strep) provides supplementary context for GI Infections</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::01_Gram_(+)_Cocci::07_Streptococcus_gallolyticus_(Group_D_Strep)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.01 01 Giardia lamblia</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>Parasitology</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
 Recognize the important clinical manifestations of protozoal and helminthic infections.
 Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::01_Protozoa_of_the_Intestinal_Tract::01_Giardia_lamblia</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.02 02 Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::01_Protozoa_of_the_Intestinal_Tract::02_Entamoeba_histolytica</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.03 03 Cryptosporidium spp.</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::01_Protozoa_of_the_Intestinal_Tract::03_Cryptosporidium_spp.</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 5.01 01 Intestinal Nematodes - Enterobius, Ancylostoma, Necator, Ascaris, Strongyloides, and Trichinella</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::05_Helminths_-_Nematodes::01_Intestinal_Nematodes_-_Enterobius,_Ancylostoma,_Necator,_Ascaris,_Strongyloides,_and_Trichinella</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro FAadd Trichuris trichiura (whipworm)</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::05_Helminths_-_Nematodes::FAadd_Trichuris_trichiura_(whipworm)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 6.01 01 Cestodes</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::06_Helminths_-_Trematodes_&amp;_Cestodes::01_Cestodes</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 6.02 02 Trematodes</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Identify the epidemiology (exposure, geographic location) that predisposes patients to protozoal and helminthic infections.
+Recognize the important clinical manifestations of protozoal and helminthic infections.
+Identify the diagnosis and treatment of clinically relevant protozoal and helminthic infections</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::06_Helminths_-_Trematodes_&amp;_Cestodes::02_Trematodes</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 2.01 01 Toxoplasma gondii</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 01 Toxoplasma gondii provides supplementary context for Parasitology</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::02_Protozoa_of_the_CNS::01_Toxoplasma_gondii</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 3.01 01 Trypanosoma cruzi</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Parasitology</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 01 Trypanosoma cruzi provides supplementary context for Parasitology</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::03_Protozoa_of_the_Blood::01_Trypanosoma_cruzi</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 5.09 09 Helicobacter pylori</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Esophagus/Stomach Disease</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 09 Helicobacter pylori provides supplementary context for Esophagus/Stomach Disease</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::09_Helicobacter_pylori</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 3.01 01 Candida albicans</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Esophagus/Stomach Disease</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 01 Candida albicans provides supplementary context for Esophagus/Stomach Disease</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::02_Fungi::03_Opportunistic_Fungal_Infections::01_Candida_albicans</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 1.02 02 Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 02 Entamoeba histolytica provides supplementary context for Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::01_Protozoa_of_the_Intestinal_Tract::02_Entamoeba_histolytica</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 1.07 07 Streptococcus gallolyticus (Group D Strep)</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 07 Streptococcus gallolyticus (Group D Strep) provides supplementary context for Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::01_Gram_(+)_Cocci::07_Streptococcus_gallolyticus_(Group_D_Strep)</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 3.01 01 Trypanosoma cruzi</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 01 Trypanosoma cruzi provides supplementary context for Intestinal Pathology I &amp; II</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::03_Protozoa_of_the_Blood::01_Trypanosoma_cruzi</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.05 05 Hepatitis A Virus (PicoRNAviridae)</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::01_RNA_(+)_Sense::05_Hepatitis_A_Virus_(PicoRNAviridae)</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 1.08 08 Hepatitis C Virus (Flaviviridae)</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::01_RNA_(+)_Sense::08_Hepatitis_C_Virus_(Flaviviridae)</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 3.12 12 Hepatitis B Viral Basics &amp; Infectious Diseases (Hepadnaviridae)</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::03_DNA::12_Hepatitis_B_Viral_Basics_&amp;_Infectious_Diseases_(Hepadnaviridae)</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 3.13 13 Hepatitis B Viral Life Cycle (Hepadnaviridae)</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::03_DNA::13_Hepatitis_B_Viral_Life_Cycle_(Hepadnaviridae)</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 4.01 01 Hepatitis A Virus (PicoRNAviridae) [Old Version]</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::04_Retired_Lessons::01_Hepatitis_A_Virus_(PicoRNAviridae)_[Old_Version]</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 4.02 02 Hepatitis B Virus (HepaDNAviridae) [Old Version]</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::04_Retired_Lessons::02_Hepatitis_B_Virus_(HepaDNAviridae)_[Old_Version]</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>sketchy-micro 4.03 03 Hepatitis C Virus (Flaviviridae) [Old Version]</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Describe the clinical features, serologic markers, and histologic findings of viral hepatitis
+Distinguish between hepatitis A, B, C, D, and E based on transmission and chronicity
+Discuss the complications of chronic hepatitis including cirrhosis and hepatocellular carcinoma</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::03_Viruses::04_Retired_Lessons::03_Hepatitis_C_Virus_(Flaviviridae)_[Old_Version]</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 1.02 02 Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 02 Entamoeba histolytica provides supplementary context for Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::01_Protozoa_of_the_Intestinal_Tract::02_Entamoeba_histolytica</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 6.02 02 Trematodes</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 02 Trematodes provides supplementary context for Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::04_Parasites::06_Helminths_-_Trematodes_&amp;_Cestodes::02_Trematodes</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 3.02 02 Aspergillus fumigatus</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 02 Aspergillus fumigatus provides supplementary context for Liver Disease I &amp; II</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::02_Fungi::03_Opportunistic_Fungal_Infections::02_Aspergillus_fumigatus</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 5.09 09 Helicobacter pylori</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 09 Helicobacter pylori provides supplementary context for Treatment of Peptic Ulcer/GERD &amp; Other GI Disorders</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::09_Helicobacter_pylori</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 5.08 08 Vibrio spp.</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>PSW: Cholera/Lactose Intolerance</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 08 Vibrio spp. provides supplementary context for PSW: Cholera/Lactose Intolerance</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::08_Vibrio_spp.</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 11.05 05 Vibrio spp. [Old Version]</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>PSW: Cholera/Lactose Intolerance</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 05 Vibrio spp. [Old Version] provides supplementary context for PSW: Cholera/Lactose Intolerance</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::11_Retired_Lessons::05_Vibrio_spp._[Old_Version]</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 2.03 03 Clostridium botulinum</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Poisoning Conference and Cases</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 03 Clostridium botulinum provides supplementary context for Poisoning Conference and Cases</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::05_Gram_(-)_Bacilli_-_Enteric_Tract::01_Klebsiella_pneumoniae,_Enterobacter_spp.,_Serratia_marcescens</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="E55" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::03_Clostridium_botulinum</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>QID 1397: Clostridium difficile infection
+QID 1398: Clostridium difficile infection
+QID 6510: Clostridium difficile infection
+QID 15049: Clostridium difficile infection
+QID 1396: Clostridium difficile infection
+QID 10401: Clostridium difficile infection</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Xref: sketchy-micro 2.04 04 Clostridium perfringens</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>Poisoning Conference and Cases</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>Cross-reference: 04 Clostridium perfringens provides supplementary context for Poisoning Conference and Cases</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>#AK_Step1_v12::#SketchyMicro::01_Bacteria::02_Gram_(+)_Bacilli::04_Clostridium_perfringens</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t>QID 1397: Clostridium difficile infection
+QID 1398: Clostridium difficile infection
+QID 6510: Clostridium difficile infection
+QID 15049: Clostridium difficile infection
+QID 1396: Clostridium difficile infection
+QID 10401: Clostridium difficile infection</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
